--- a/regulatory-compliance/cloud-foundation/9.1/cyber-essentials/vcf-91-companion-cyber-essentials.xlsx
+++ b/regulatory-compliance/cloud-foundation/9.1/cyber-essentials/vcf-91-companion-cyber-essentials.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="190" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Version 910-20260612-01</t>
+          <t>Version 910-20260623-01</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,16 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Additional Resources</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
-This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+          <t>This is one of a library of companion guides that map VMware Cloud Foundation and its advanced services to security and compliance frameworks. For each framework, the guide is published as a spreadsheet, a CSV data file, a Markdown document, and a PDF, together with a Security Configuration Guide crosswalk that identifies the VCF technical hardening settings relevant to that framework. The companion guide library, the VMware Cloud Foundation Security Configuration Guide, and related security documentation, sample scripts, and Q&amp;A are available at https://brcm.tech/vcf-security.</t>
         </is>
       </c>
     </row>
@@ -554,12 +553,28 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
+This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Copyright (c) CA, Inc. All rights reserved.
 You are hereby granted a non-exclusive, worldwide, royalty-free license under CA, Inc.'s copyrights to use, copy, modify, and distribute this software in source code or binary form for use in connection with CA, Inc. products.
@@ -568,16 +583,16 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Third Party Identifiers and Mappings</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>This document includes regulatory compliance and security control identifiers from external sources as a convenience to end users. This does not constitute endorsement, in either direction.
 There is not a one-to-one mapping of product capabilities to third-party controls. A product capability, or set of capabilities, may be applicable to multiple controls. Conversely, a control may be satisfied with the use of multiple capabilities.
@@ -970,13 +985,13 @@
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) 9.1 provides structured user provisioning and de-provisioning capabilities that support a formal access rights lifecycle for both local accounts and directory-integrated users.
-User accounts in DSM are managed through two identity sources: local users created and managed within the DSM platform itself, and LDAP/LDAPS users authenticated through an enterprise directory service such as Active Directory. DSM can be configured to use one or both identity sources independently. The first local user account is the DSM administrator, created during deployment of the DSM Provider Appliance. That account is mandatory and cannot be deleted. All subsequent local user creation requires administrator credentials, meaning only authorized personnel can add new accounts to the system.
-When provisioning a local user, an administrator must specify the user's role, email address, and password through the DSM user creation workflow, accessible in the vSphere Client or the DSM UI. DSM's two built-in roles define the access scope: the Administrator role manages the platform, namespaces, and other users, while the User role creates and maintains individual databases. Namespace access is assigned at user creation. Administrators can modify both role assignments and namespace access for existing local users through the user management interface. Administrators can delete local user accounts when removal is the appropriate de-provisioning action. Alternatively, to prohibit a user's access to DSM while keeping databases running, an administrator can reset the user's password and delegate database management to a different user.
-For directory-integrated environments, DSM supports LDAPS authentication and allows assignment of roles to Directory Service Groups, enabling group-based access control for LDAP users. When a user's directory group membership changes, their effective access within DSM reflects the group role assignment.
-For SQL Server databases provisioned within VCF Automation, DSM data service policies define the allowed user types for databases created under the policy. Administrators can configure policies to permit Windows Principal authentication using Active Directory credentials, SQL User authentication using standard SQL Server login credentials, or both. For automated Active Directory integration, DSM requires a privileged Active Directory account with permissions to write service principal names (SPNs) and perform dynamic DNS updates. SQL Server databases map the dbo user, the database object owner, to administrator-controlled identities.
-The Permissions view in the DSM dashboard provides a consolidated interface for creating, monitoring, and managing all configured user accounts and directory service groups. Because user login precedence between local and LDAPS accounts must be managed deliberately to avoid authentication conflicts, organizations should establish clear provisioning procedures that address the ordering and priority rules DSM applies.
-DSM's mechanisms support the technical registration and de-registration workflow but do not themselves constitute a formal process. The control's requirement for governance-level procedures governing access rights assignment extends to organizational approval workflows, access review cycles, and documented registration practices that operate outside the platform. Organizations must establish these processes independently, using DSM's user management capabilities as the technical enforcement layer.</t>
+          <t>VMware Data Services Manager (DSM) applies role-based access controls that restrict software installation and activation activities to users with explicitly assigned privileged status. Several layers of privilege enforcement exist across the platform's operational surface.
+Deploying the DSM Provider Appliance requires a user with the vSphere Administrator role, which has exclusive responsibility for deploying the appliance and managing DSM VM updates. This prerequisite is enforced at the deployment step and cannot be bypassed by standard user accounts.
+Within DSM, activating or deactivating supported data service versions (such as PostgreSQL, MySQL, or SQL Server) is restricted to DSM administrators. Standard DSM Users cannot activate new data service versions. SQL Server instance provisioning and server-level configuration management, including Active Directory integration and high availability configuration, are also restricted to DSM administrators only.
+At the database level, activating or deactivating PostgreSQL extensions requires the PostgreSQL SUPERUSER role. Extensions cannot be added by ordinary database users, which restricts the installation of additional database-level software components to specifically privileged accounts. For MySQL databases, DSM revokes the create and update privileges on objects in the mysql system schema for database users, preventing unauthorized modification of system-level components. For SQL Server databases, DSM grants the cluster administrator login restricted read-only privileges and specific ALTER privileges for server management and auditing, rather than full privileges. The dsm_db_user custom database role denies TAKE OWNERSHIP on the database to prevent privilege escalation.
+The DSM administrator UI includes a Permissions view where administrators create, monitor, and manage user accounts and role assignments. DSM User role assignments can be scoped to one or more specific Supervisor namespaces, further limiting what operations a given user can perform within the platform.
+Configuring infrastructure policies, which govern where and how database resources are provisioned, requires a vSphere administrator with appropriate DSM permissions. These policies are enforced automatically during provisioning operations.
+The broader requirement to prohibit unauthorized software installations across all systems and workloads in an environment requires organizational processes and controls at the infrastructure layer that extend beyond DSM's scope.</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
@@ -986,11 +1001,11 @@
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) includes a native user management system accessible through Administration &gt; Accounts &gt; Users on the Avi Controller. Administrators can create local user accounts, assign each account a specific role and tenant scope, and remove accounts when access is no longer required. Each user account stores role and tenant assignments directly, supporting granular scoping of permissions per deployment.
-Avi's RBAC model supports both local user accounts validated against an internal database and remote authentication through LDAP or SAML. Auth Mapping Profiles extend the RBAC model by binding external directory group membership to specific Avi roles and tenants at login time. When a user's group membership changes in the directory, the Auth Mapping Profile applies the updated role and tenant assignments on the next login, without requiring manual changes inside Avi. Multiple Auth Mapping Profile rules can be configured so that a single user's LDAP or SAML group memberships determine distinct roles across multiple tenants simultaneously. SAML integration with Microsoft Active Directory Federation Services (ADFS) is also supported, with configurable issuance authorization rules that control which users may access the relying party.
-Avi Controller allows creation of custom roles according to specific access requirements when predefined roles do not fit an account's needs. The Tenant-Admin role can be scoped so that tenant administrators can create, update, and delete cloud infrastructure within their tenant boundary without affecting other tenants. Avi GSLB extends user provisioning to global load balancing by supporting the creation of non-admin users with assigned roles for granular access control across GSLB deployments. The Avi License Hub also supports role-based access control by assigning roles to individual users or groups defined in an external identity provider.
-User accounts are attached by default to the Default-User-Account-Profile, and administrators can create new user account profiles with different concurrent session thresholds to meet organizational security requirements.
-Organizations should establish and document formal procedures for user registration, access approval, and de-registration to govern how and when accounts are created or removed in Avi. The technical mechanisms Avi provides, including account creation and deletion, role assignment, and directory integration via Auth Mapping Profiles, support a formal lifecycle process but do not replace the organizational procedures the control requires.</t>
+          <t>VMware Avi Load Balancer provides technical mechanisms for enforcing software license quota restrictions within its Controller management plane. The Controller enforces a configurable global upper limit on license consumption at the system level through the license quota limit setting, accessible under Administration &gt; Licensing. When that limit is reached, provisioning of new Service Engines is blocked, directly capping usage at the configured boundary and rejecting licensing operations that would exceed it.
+The license quota hierarchy extends to multiple levels depending on the licensing model in use. In the On-premise License Hub model, limits can be set at the system, tenant, and Service Engine Group levels; operations are rejected when these quotas are exceeded. In the Cloud Licensing model, limits are supported only at the system level; tenant and Service Engine Group limits are not available in that configuration. This distinction is important for organizations deploying Avi in hybrid or cloud-connected environments.
+The Avi Cloud Console provides centralized license management across registered License Hub deployments, including a Maximum Allowed Licenses setting accessible under Administration &gt; Licensing. Access to licensing operations within the Cloud Console is governed by Role-Based Access Control (RBAC): Full Access users with User Administrator or Product Administrator roles can register or deregister License Hubs, add or remove licenses, and perform allocation tasks, while Read-Only users cannot perform these actions. This RBAC separation helps restrict who can modify license entitlements.
+For high-security or air-gapped environments, the Avi License Hub supports Private Mode operation. In this mode, a license file is downloaded from Avi Cloud Console and imported together with the private key used to generate it, removing the dependency on external network connectivity for license validation.
+Organizations remain responsible for the procurement, tracking, and auditing processes that these technical controls support. Avi's quota enforcement covers the application delivery controller itself; software licenses for the broader VCF stack, operating systems, and other application workloads are managed through platform-level and organizational processes outside Avi's scope.</t>
         </is>
       </c>
     </row>
@@ -1012,46 +1027,27 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several platform capabilities that support malicious code protection, though organizations must deploy additional tools to achieve full antimalware coverage across endpoints.
-At the hypervisor layer, VMware ESX supports Secure Boot and code signing to restrict unauthorized code from executing on hosts. Trusted Platform Module (TPM) support enables boot-time integrity measurement, and VMware vCenter provides APIs to retrieve TPM event logs for validating boot-time measurements or configuring firmware trust with an attestation service. Administrators can verify that hosts have booted in a known good configuration by checking TPM device status and event logs through the vCenter trusted infrastructure API. ESX host TPM modules must be verified as running the latest 2.0 firmware, and if not in use, disabled in the BIOS. Virtual machines can be configured with UEFI firmware for guest operating system boot integrity. Windows guest operating systems support Virtualization Based Security (VBS), which enables Device Guard to help prevent malware from running and Credential Guard to protect credential secrets; these features are configurable through Group Policy on VMs with ESX 6.7 or later compatibility. Virtual machines can also have the Guest Integrity (GI) security device enabled through the VMware Host Client, which is the platform foundation for VMware AppDefense.
-The vSphere Security Configuration Guide provides hardening recommendations for ESX hosts, including configuring authentication and authorization settings, disabling unnecessary services, and enabling security features like Secure Boot and TPM. These configuration baselines are industry-standard best practices for host hardening.
-vSphere Lifecycle Manager and VCF Operations Configuration Profiles maintain desired-state configuration for ESX hosts. Configuration Drifts in VCF Operations provides a proactive method to monitor configuration changes and identify when vCenter instances and vSphere clusters deviate from their approved baselines. Drift status is updated through a collection cycle that runs every 8 hours. This helps identify when host software or configuration has been modified from its approved state, which can indicate unauthorized changes or tampering.
-VCF's networking layer, NSX, supports integration with third-party endpoint protection solutions for virtual machine security. The platform documentation references specific partner integrations including Symantec Endpoint Protection and ESET Antivirus/Security software, which provide anti-malware, intrusion prevention, and firewall capabilities for guest virtual machines. NSX App IDs can be used in conjunction with these third-party solutions for network management and security policy enforcement. Organizations can implement security groups, define security policies, and use NSX's integration with third-party security solutions for virtual machine protection.
-NSX Guest Introspection provides an agent-based framework that supports endpoint security within virtual machines. The Guest Introspection Agent must be installed and running in each guest VM, and logged-in users should not have the privilege to remove or stop the agent. This architecture enables third-party security solutions to inspect guest operating system activity without requiring agents to be installed directly on the hypervisor. The security and integrity of the guest operating system must be maintained for these integrations to function correctly.
-For container workloads, the VCF CLI supports cosign signature verification for container images through the imgpkg tool, which enables finding and copying cosign signatures. Image pull authentication through imagePullSecrets restricts container image pulls to authenticated private registries. Plugin discovery image signature verification is supported, with configurable public key paths for the cosign verifier. These capabilities help restrict deployment of images that have been tampered with.
-VCF Operations supports the deployment and monitoring of agents on endpoint virtual machines, with guest operation privileges required to install agents. Automated software update capabilities in vCenter help keep systems current with security patches, reducing the window of exposure to known malware exploits.
-For organizations that deploy VMware vDefend as an add-on to VCF, distributed malware prevention capabilities become available. The NSX Application Platform hosts the Malware Prevention for vDefend feature, which can be deployed from the Local Manager UI in NSX Federation environments. When host clusters are activated for Distributed Malware Prevention, a service virtual machine (SVM) is deployed on each host to perform malware scanning. vDefend also supports IDS/IPS capabilities alongside distributed malware prevention. The DistributedMps runbook is available to verify the health of the Malware Prevention Service pipeline and diagnose issues such as protection not working on a particular VM or certain files not being scanned.
-Malware prevention activities generate log data for audit and forensic purposes. The Malware Prevention for vDefend feature writes log files that can be used for troubleshooting and security monitoring, and remote logging can be configured on the malware prevention SVMs for centralized log collection.
-VMware Private AI Services (PAIS) includes model validation capabilities that scan machine learning model files for malicious content before they are accepted into a Model Gallery. The validation runs as a sandbox process on Deep Learning VMs and covers integrity verification through hash code checking, malware scanning, serialization attack scanning, and inference behavior testing with NVIDIA Triton Inference Server. Both the malware and serialization checks run as part of the validation workflow required before a model can be uploaded to a Model Gallery and made available to downstream model endpoints, knowledge bases, or AI agents.
-Machine learning model files are a category of artifact that traditional endpoint security tools may not inspect. Serialized models in formats such as Python pickle files can carry executable payloads that activate when an application or researcher loads the model. The PAIS Model Gallery intake workflow treats this upload boundary as a security checkpoint, requiring each artifact to pass hash, malware, serialization, and inference behavior tests before it is published for use. PAIS guidance also directs organizations to distribute only models that have been validated internally on a Deep Learning VM rather than pulling artifacts directly from the Internet, where models may contain malicious code or be tuned for malicious behavior. The validation is operated by MLOps engineers, who confirm that onboarded models meet the organization's security, privacy, and technical requirements.
-For platform-level malware protection covering virtual machines, VMware ESX hosts, and general workloads running on the PAIS infrastructure, organizations rely on VCF platform controls and, where deployed, VMware vDefend. PAIS adds the specialized scanning layer applied to AI model artifacts at the point of intake, addressing a threat surface that general-purpose antimalware tools do not typically cover.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides multiple layers of malicious code detection and prevention through its Malware Prevention Service and IDS/IPS capabilities. Together these address the detection aspect of this control directly and contribute to the eradication aspect by restricting malicious code from executing and spreading across the network.
-The Malware Prevention Service deploys as a service virtual machine (SVM) on each host in a cluster, with Guest Introspection thin agents installed on each protected guest VM. This architecture separates the detection engine from the protected workload, giving the service visibility into file activity, process execution, and network events from outside the guest. On Linux guests, a File and Network Agent handles file and network traffic introspection. A Host Agent (MUX) component running on ESX hosts supports the Guest Introspection functionality.
-The service detects both known and unknown malicious files, including zero-day threats. Supported file categories include Windows executables (.exe, self-extracting), Linux executables (.elf), installer files (.msi), and shortcut files (.lnk), among others. When a file is analyzed, Malware Prevention assigns a verdict and classifies the threat by malware class (virus, trojan horse, worm, adware, ransomware, spyware) and malware family. A single detection event can be associated with multiple malware families and classes. Upon detection, the service can take direct remediation actions, including denying access to suspicious files or deleting files identified as malicious. An allowlist capability enables administrators to override verdicts for files known to be legitimate, suppressing false positives without disabling broader detection.
-Beyond file-based detection, Malware Prevention Service includes fileless malware detection to identify attacks that operate entirely within system memory using existing binaries and in-memory operations such as PowerShell or VBScript, without leaving executable artifacts on disk. The service monitors Indicators of Compromise including process command lines, process hashes, process execution trees, and in-memory executions. In-memory script buffer executions are scored for threat severity and assigned a verdict of malicious or suspicious, with the associated malware family and class displayed on the Malware Prevention Dashboard.
-When malware is detected, the service extracts artifacts and in-memory script buffers that security teams can use to define incidents of compromise and create new detection rules for similar future threats. This extends malware coverage as new threat patterns are identified within the environment.
-The Malware Prevention Dashboard in Security Services Platform aggregates detection events for malicious files, suspicious files, and uninspected files over configurable time periods. Each unique file is tracked by hash, and events can be filtered by verdict criteria. This centralized visibility allows security teams to identify malware incidents, track detection trends, and coordinate eradication efforts across the virtualized environment.
-vDefend IDS/IPS provides signature-based and behavioral intrusion detection and prevention at the distributed firewall level, complementing Malware Prevention with network-layer detection of malware delivery attempts, command-and-control communications, and lateral movement patterns associated with malware infections. IDS/IPS operates at the virtual network interface level, providing visibility into east-west traffic between workloads that perimeter security tools cannot inspect.
-While vDefend provides strong detection and file-level remediation capabilities, complete eradication of malicious code from infected guest operating systems typically requires endpoint security agents operating inside the guest. vDefend restricts malware from spreading across the network and blocks or removes detected malicious files, but cleaning an already-infected system requires host-level remediation tooling.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1076,17 +1072,12 @@
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer contributes to malicious code protection at the application delivery layer through WAF-based payload inspection, IP Reputation threat intelligence, Application Rules, and Bot Management.
-The Avi WAF inspects inbound HTTP/HTTPS request bodies and parameters against signature-based rules, including ModSecurity rules, to detect and block exploit payloads, injection attacks, and known malware delivery patterns. WAF rules are configurable per virtual service and can be tuned to reduce false positives while maintaining coverage of malicious traffic patterns. Configuration is managed through the Avi Controller UI under the WAF Policy section for each virtual service.
-The Application Rules service, available through Avi Cloud Console Live Security Threat Intelligence, provides automatically updated WAF rules targeting known vulnerabilities with CVE mappings across more than 5,000 applications, including WordPress, Drupal, and Apache. These rules are pushed automatically to Avi Controllers, reducing the window between vulnerability disclosure and protection.
-Avi's IP Reputation service provides a threat intelligence feed that classifies IP addresses known to be infected with malware or identified as contacting malware distribution points (threat category code 6). The service also identifies IP addresses known to distribute malware, shell code, rootkits, worms, or viruses, including Windows exploit IP addresses. An "All threats" classification (threat category code 32) can be applied to block any suspicious IP addresses at the application delivery layer. IP Reputation data is synchronized via Avi Cloud Services and can be referenced in virtual service policies to block malicious source traffic before it reaches protected workloads. This is configured under Administration &gt; External Services &gt; Cloud Services.
-Avi Bot Management provides a default System-BotDetectionPolicy that can be bound to virtual services to detect and mitigate malicious bots used in online fraud, credential stuffing, and automated data scraping. Bot Management performs heuristic scanning of User-Agent strings to detect malicious patterns such as SQL injections, marking such requests as bad bot of type web attack. In Kubernetes deployments, the Avi Kubernetes Operator (AKO) supports assigning a BotDetectionPolicy to virtual services via the botPolicyRef parameter, extending bot detection to Kubernetes ingress workloads.
-Avi WAF does not include built-in virus or file-content malware scanning. Avi documentation explicitly recommends deploying a dedicated virus and malware scanning tool on the upload directories of protected applications to detect and mitigate malicious uploads, including uploads that may bypass WAF inspection. Malware detection and eradication for workloads running behind Avi is the responsibility of endpoint protection tools deployed on those workloads. Organizations should configure WAF policies, Application Rules, IP Reputation, and Bot Management on Avi virtual services while also deploying dedicated antimalware solutions on application workloads and their supporting infrastructure.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
